--- a/src/DataEngine/DataFiles/Config.xlsx
+++ b/src/DataEngine/DataFiles/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akshay.Kumar\Desktop\AutomationTestData\mycomporium-tests-2\src\DataEngine\DataFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\automation_practice_demo\src\DataEngine\DataFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83D2843-B7F1-4644-BC74-E9E6CD9E26A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF27A0EC-C9B9-4CFD-B868-95D7D0118E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="927" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="927" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -2763,9 +2763,6 @@
     <t>Desktop_Comporium_New,Desktop_LocationMaster</t>
   </si>
   <si>
-    <t>MyComporium</t>
-  </si>
-  <si>
     <t>Show Blocked Test Cases in Report</t>
   </si>
   <si>
@@ -2776,7 +2773,10 @@
     <t>Browser Zoom Level</t>
   </si>
   <si>
-    <t>Desktop_MyComporium,Desktop_AccessPoint,Desktop_Shop,Desktop_AdminPortal</t>
+    <t xml:space="preserve">AutomationPractice </t>
+  </si>
+  <si>
+    <t>Desktop_ContentCatalog</t>
   </si>
 </sst>
 </file>
@@ -3370,16 +3370,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="93.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="93.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3390,18 +3390,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C2" s="23" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="24" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="23" t="s">
         <v>4</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="24" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
         <v>6</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
         <v>7</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="24" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="23" t="s">
         <v>8</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="24" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="24" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>10</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="24" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
         <v>255</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="24" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="23" t="s">
         <v>12</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="23" t="s">
         <v>14</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="24" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="23" t="s">
         <v>16</v>
       </c>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="24" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="23" t="s">
         <v>18</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="24" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="24" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="23" t="s">
         <v>21</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="24" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="23" t="s">
         <v>128</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="24" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="23" t="s">
         <v>24</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="24" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="23" t="s">
         <v>26</v>
       </c>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="I16" s="27"/>
     </row>
-    <row r="17" spans="1:3" s="24" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="23" t="s">
         <v>28</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="24" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="23" t="s">
         <v>29</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="24" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="24" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="23" t="s">
         <v>30</v>
       </c>
@@ -3596,18 +3596,18 @@
         <v>247</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="24" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="24" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A20" s="23" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="24" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="23" t="s">
         <v>32</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="24" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" s="24" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A22" s="23" t="s">
         <v>35</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="24" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" s="24" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="23" t="s">
         <v>37</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="23" t="s">
         <v>270</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>284</v>
       </c>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>34</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A27" s="23" t="s">
         <v>287</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="23" t="s">
         <v>289</v>
       </c>
@@ -3693,20 +3693,20 @@
         <v>290</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="16" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>301</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>302</v>
       </c>
       <c r="B30" s="36">
         <v>0.8</v>
@@ -3829,15 +3829,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.1796875" customWidth="1"/>
+    <col min="4" max="4" width="33.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>78</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>87</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>89</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>91</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>92</v>
       </c>
@@ -3983,14 +3983,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="68.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>94</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>95</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>97</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>75</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>192</v>
       </c>
@@ -4074,14 +4074,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="2" max="2" width="50.42578125" customWidth="1"/>
-    <col min="3" max="3" width="72.7109375" customWidth="1"/>
+    <col min="1" max="1" width="21.453125" customWidth="1"/>
+    <col min="2" max="2" width="50.453125" customWidth="1"/>
+    <col min="3" max="3" width="72.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>77</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>75</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>78</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>102</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>104</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>106</v>
       </c>
@@ -4176,14 +4176,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>78</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>110</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>102</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>112</v>
       </c>
@@ -4278,14 +4278,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="58.42578125" customWidth="1"/>
+    <col min="3" max="3" width="58.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>116</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>118</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>119</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>120</v>
       </c>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="D6" s="31"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>121</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>123</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>124</v>
       </c>
@@ -4410,14 +4410,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="92.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.42578125" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="92.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>126</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>124</v>
       </c>
@@ -4480,14 +4480,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.5703125" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>126</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>124</v>
       </c>
@@ -4544,31 +4544,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:O182"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>4</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="4" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>160</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>154</v>
       </c>
@@ -4746,26 +4746,26 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="L7" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="L8" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="9" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>39</v>
       </c>
@@ -4784,30 +4784,30 @@
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
         <v>226</v>
       </c>
@@ -4826,28 +4826,28 @@
       <c r="N26" s="13"/>
       <c r="O26" s="13"/>
     </row>
-    <row r="27" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="33" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11"/>
     </row>
-    <row r="38" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
         <v>48</v>
       </c>
@@ -4866,30 +4866,30 @@
       <c r="N38" s="13"/>
       <c r="O38" s="13"/>
     </row>
-    <row r="39" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="49" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A50" s="13" t="s">
         <v>48</v>
       </c>
@@ -4914,7 +4914,7 @@
       <c r="N50" s="13"/>
       <c r="O50" s="13"/>
     </row>
-    <row r="51" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="53" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>161</v>
       </c>
@@ -4953,23 +4953,23 @@
         <v>215</v>
       </c>
     </row>
-    <row r="54" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="55" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -4986,22 +4986,22 @@
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
     </row>
-    <row r="63" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="65" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="66" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="67" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="68" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="69" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="70" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="73" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="11" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A74" s="13"/>
       <c r="B74" s="13"/>
       <c r="C74" s="13"/>
@@ -5018,22 +5018,22 @@
       <c r="N74" s="13"/>
       <c r="O74" s="13"/>
     </row>
-    <row r="75" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="81" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="82" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="84" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="85" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="11" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="86" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
@@ -5050,22 +5050,22 @@
       <c r="N86" s="13"/>
       <c r="O86" s="13"/>
     </row>
-    <row r="87" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="88" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="89" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="90" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="92" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="93" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="94" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="95" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="96" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="97" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="98" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A98" s="13" t="s">
         <v>80</v>
       </c>
@@ -5088,7 +5088,7 @@
       <c r="N98" s="13"/>
       <c r="O98" s="13"/>
     </row>
-    <row r="99" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>81</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>147</v>
       </c>
@@ -5110,24 +5110,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="102" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="103" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="104" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="105" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="106" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="107" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="109" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A109" s="11" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A110" s="13" t="s">
         <v>99</v>
       </c>
@@ -5146,30 +5146,30 @@
       <c r="N110" s="13"/>
       <c r="O110" s="13"/>
     </row>
-    <row r="111" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="114" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="115" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="116" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="117" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="118" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="119" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="120" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="121" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A121" s="11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="122" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A122" s="13"/>
       <c r="B122" s="13"/>
       <c r="C122" s="13"/>
@@ -5186,15 +5186,15 @@
       <c r="N122" s="13"/>
       <c r="O122" s="13"/>
     </row>
-    <row r="123" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="124" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="125" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="11" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="127" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A127" s="13"/>
       <c r="B127" s="13"/>
       <c r="C127" s="13"/>
@@ -5211,27 +5211,27 @@
       <c r="N127" s="13"/>
       <c r="O127" s="13"/>
     </row>
-    <row r="128" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="129" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="130" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="131" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="132" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="133" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="134" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="135" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A135" s="11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="136" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A136" s="13"/>
       <c r="B136" s="13"/>
       <c r="C136" s="13"/>
@@ -5248,22 +5248,22 @@
       <c r="N136" s="13"/>
       <c r="O136" s="13"/>
     </row>
-    <row r="137" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="138" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="139" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="140" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="141" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="142" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="143" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="144" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="145" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="146" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="147" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A147" s="11" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="148" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A148" s="13" t="s">
         <v>114</v>
       </c>
@@ -5288,7 +5288,7 @@
       <c r="N148" s="13"/>
       <c r="O148" s="13"/>
     </row>
-    <row r="149" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>115</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="150" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>151</v>
       </c>
@@ -5316,20 +5316,20 @@
         <v>587</v>
       </c>
     </row>
-    <row r="151" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="152" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="153" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="154" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="155" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="156" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="157" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="158" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="159" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="160" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A160" s="13"/>
       <c r="B160" s="13"/>
       <c r="C160" s="13"/>
@@ -5346,22 +5346,22 @@
       <c r="N160" s="13"/>
       <c r="O160" s="13"/>
     </row>
-    <row r="161" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="162" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="163" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="164" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="165" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="166" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="167" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="168" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="169" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="170" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="171" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A171" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="172" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" s="14" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A172" s="13"/>
       <c r="B172" s="13"/>
       <c r="C172" s="13"/>
@@ -5378,16 +5378,16 @@
       <c r="N172" s="13"/>
       <c r="O172" s="13"/>
     </row>
-    <row r="173" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="177" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="178" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="179" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="180" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="181" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="182" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="174" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="175" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="176" spans="1:15" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="177" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="178" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="179" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="180" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="181" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="182" outlineLevel="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5397,13 +5397,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>272</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
         <v>274</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>275</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>283</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>277</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>279</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>282</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>281</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>280</v>
       </c>
@@ -5485,14 +5485,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="37.7109375" style="16" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.7265625" customWidth="1"/>
+    <col min="5" max="5" width="37.7265625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>39</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>166</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>166</v>
       </c>
@@ -5560,10 +5560,10 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E9"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E10"/>
     </row>
   </sheetData>
@@ -5592,19 +5592,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" customWidth="1"/>
+    <col min="4" max="4" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>46</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="17">
         <v>2</v>
       </c>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="17">
         <v>3</v>
       </c>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="17">
         <v>4</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="17">
         <v>6</v>
       </c>
@@ -5789,21 +5789,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="48" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
-    <col min="10" max="10" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" customWidth="1"/>
+    <col min="10" max="10" width="29.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>46</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="17">
         <v>2</v>
       </c>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="17">
         <v>3</v>
       </c>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="17">
         <v>4</v>
       </c>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -6018,15 +6018,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.42578125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.453125" style="16" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>76</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F6" t="s">
         <v>266</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F7" t="s">
         <v>267</v>
       </c>
@@ -6111,14 +6111,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.28515625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="42.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>77</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>75</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>78</v>
       </c>
@@ -6175,14 +6175,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
